--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_17/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_17/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55.75718741284847</v>
+        <v>58.16936864108953</v>
       </c>
       <c r="B2" t="n">
-        <v>168.9818750251465</v>
+        <v>106.8650710207591</v>
       </c>
       <c r="C2" t="n">
-        <v>49.0310671394415</v>
+        <v>45.42231645021892</v>
       </c>
       <c r="D2" t="n">
-        <v>12.50609466930299</v>
+        <v>12.73550107390722</v>
       </c>
       <c r="E2" t="n">
-        <v>2.208715832970053</v>
+        <v>4.841317111729771</v>
       </c>
       <c r="F2" t="n">
-        <v>7.51079224502173</v>
+        <v>7.907328652079627</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3257358813324761</v>
+        <v>0.2717713983098701</v>
       </c>
       <c r="H2" t="n">
-        <v>-7.000732344004297e-05</v>
+        <v>-0.001544738293483415</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5925536189842213</v>
+        <v>-0.5949754526708404</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.293545373215064</v>
+        <v>-0.2980087715114788</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0006583052936545616</v>
+        <v>-0.002627528927827589</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2915100779193311</v>
+        <v>-0.3112702648081714</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.09203430296970784</v>
+        <v>-0.0012326800477655</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999998537602</v>
+        <v>99.99997840908406</v>
       </c>
       <c r="B3" t="n">
-        <v>113.2000249658273</v>
+        <v>105.9586081507886</v>
       </c>
       <c r="C3" t="n">
-        <v>48.78482948598962</v>
+        <v>45.536512869931</v>
       </c>
       <c r="D3" t="n">
-        <v>7.045202507403623</v>
+        <v>8.067775731938623</v>
       </c>
       <c r="E3" t="n">
-        <v>2.810295006776434</v>
+        <v>4.995265682031392</v>
       </c>
       <c r="F3" t="n">
-        <v>15.80321710511676</v>
+        <v>16.12100405309242</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03917983792228466</v>
+        <v>0.03858805637370515</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8168359347642912</v>
+        <v>-0.7912615357747678</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8956231928925202</v>
+        <v>-0.8833552224062257</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9256119041027344</v>
+        <v>-0.9116785295758295</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.001752602204537199</v>
+        <v>-5.676920253234937e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6220069728847939</v>
+        <v>-0.5874998461647239</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07709765224310053</v>
+        <v>-0.02614826253040103</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55.75718741284847</v>
+        <v>65.11008506664119</v>
       </c>
       <c r="B4" t="n">
-        <v>168.9818750251465</v>
+        <v>110.4752331396558</v>
       </c>
       <c r="C4" t="n">
-        <v>49.0310671394415</v>
+        <v>46.27625612191387</v>
       </c>
       <c r="D4" t="n">
-        <v>12.50609466930299</v>
+        <v>12.39076959410245</v>
       </c>
       <c r="E4" t="n">
-        <v>2.198488073504175</v>
+        <v>4.164217665889569</v>
       </c>
       <c r="F4" t="n">
-        <v>7.51079224502173</v>
+        <v>9.089553454955164</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3257358813324761</v>
+        <v>0.1784896519461402</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.000732344004297e-05</v>
+        <v>-0.2747036835616584</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5925536189842213</v>
+        <v>-0.6815535213430368</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.293545373215064</v>
+        <v>-0.5394764207764987</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0006583052936545616</v>
+        <v>-0.02749692770680833</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2915100779193311</v>
+        <v>-0.3389093560998184</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09203430296970784</v>
+        <v>-0.1875467902357532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56.256013401407</v>
+        <v>69.06974438780406</v>
       </c>
       <c r="B5" t="n">
-        <v>98.64587306446256</v>
+        <v>97.2553202857172</v>
       </c>
       <c r="C5" t="n">
-        <v>48.8088180455308</v>
+        <v>45.42137069205684</v>
       </c>
       <c r="D5" t="n">
-        <v>7.095711744906306</v>
+        <v>11.99851912708387</v>
       </c>
       <c r="E5" t="n">
-        <v>2.669747997856406</v>
+        <v>4.833722024778629</v>
       </c>
       <c r="F5" t="n">
-        <v>7.704976779081051</v>
+        <v>9.687260291682234</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2913455134530316</v>
+        <v>0.1431387511508695</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.042926750257858</v>
+        <v>-0.3904951310470838</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6089366174206413</v>
+        <v>-0.7220004446851689</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3365167005984443</v>
+        <v>-0.6345194721833547</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02608388922563248</v>
+        <v>-0.01218090571275668</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6235434158550841</v>
+        <v>-0.3671219287631039</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.07873589347258211</v>
+        <v>-0.001026332812400638</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89.98963056984542</v>
+        <v>92.28557252571409</v>
       </c>
       <c r="B6" t="n">
-        <v>97.18040730913741</v>
+        <v>36.38389035982939</v>
       </c>
       <c r="C6" t="n">
-        <v>48.88642204782933</v>
+        <v>45.41950550720777</v>
       </c>
       <c r="D6" t="n">
-        <v>8.623289056340248</v>
+        <v>8.588871469171051</v>
       </c>
       <c r="E6" t="n">
-        <v>3.730739533475267</v>
+        <v>4.996667850255492</v>
       </c>
       <c r="F6" t="n">
-        <v>13.53518400415967</v>
+        <v>14.14665001396278</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05624019536336329</v>
+        <v>0.05060257380635878</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7526872792779643</v>
+        <v>-0.7396171109449832</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8656650325609854</v>
+        <v>-0.8603911259250427</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8893491579406191</v>
+        <v>-0.8818992860045967</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.00943430781117327</v>
+        <v>-0.01919996371795773</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5472288153283179</v>
+        <v>-0.0009585238857231134</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08403567297455536</v>
+        <v>-0.0006193833907876256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91.29327178361177</v>
+        <v>70.15189140044605</v>
       </c>
       <c r="B7" t="n">
-        <v>160.8518003996956</v>
+        <v>110.6287042954644</v>
       </c>
       <c r="C7" t="n">
-        <v>48.79758415450376</v>
+        <v>46.27627513985092</v>
       </c>
       <c r="D7" t="n">
-        <v>8.414783670923883</v>
+        <v>12.38102074721889</v>
       </c>
       <c r="E7" t="n">
-        <v>2.651321323988727</v>
+        <v>4.039167644522259</v>
       </c>
       <c r="F7" t="n">
-        <v>13.81049660082951</v>
+        <v>10.05122343630701</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05349233707044165</v>
+        <v>0.1357650922134009</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7626690567283706</v>
+        <v>-0.4170094615705512</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8701943817524752</v>
+        <v>-0.7313956896034014</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8952207396610379</v>
+        <v>-0.6553865057751813</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.002507848625149109</v>
+        <v>-0.1063398346617197</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5569671060979767</v>
+        <v>-0.374832226228178</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07796870178621183</v>
+        <v>-0.1875509396038379</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>58.27901430425241</v>
+        <v>63.01262057641416</v>
       </c>
       <c r="B8" t="n">
-        <v>180.9351093974955</v>
+        <v>100.8223607224337</v>
       </c>
       <c r="C8" t="n">
-        <v>48.82299196076615</v>
+        <v>45.44352289002451</v>
       </c>
       <c r="D8" t="n">
-        <v>12.4398243637124</v>
+        <v>12.37614457638656</v>
       </c>
       <c r="E8" t="n">
-        <v>2.21398949645624</v>
+        <v>4.330861742184812</v>
       </c>
       <c r="F8" t="n">
-        <v>7.893774824246145</v>
+        <v>8.650334156459969</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2755615701201725</v>
+        <v>0.2011456766776151</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1223648108094093</v>
+        <v>-0.211081454105862</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6312941986001863</v>
+        <v>-0.6619897021389524</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4060088188412276</v>
+        <v>-0.486639060416905</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.02535825247189106</v>
+        <v>-0.0004020694452541209</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3103483006449572</v>
+        <v>-0.3357797879650285</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07970386707190767</v>
+        <v>-0.005859539641711875</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74.25908324608523</v>
+        <v>78.80220959781666</v>
       </c>
       <c r="B9" t="n">
-        <v>131.6583549274469</v>
+        <v>123.9881433289821</v>
       </c>
       <c r="C9" t="n">
-        <v>48.5939537034</v>
+        <v>45.41890176741921</v>
       </c>
       <c r="D9" t="n">
-        <v>10.74537087458507</v>
+        <v>11.05148315767015</v>
       </c>
       <c r="E9" t="n">
-        <v>3.746145037827446</v>
+        <v>4.813913624888698</v>
       </c>
       <c r="F9" t="n">
-        <v>10.45111056865772</v>
+        <v>11.48939092905428</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1116926995262359</v>
+        <v>0.08857158610207179</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.568981064393744</v>
+        <v>-0.5853537243869357</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7887887717182301</v>
+        <v>-0.7951034700616307</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7689847622461025</v>
+        <v>-0.7808021506446114</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.02598563147838991</v>
+        <v>-0.03411568094294109</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4297205299297026</v>
+        <v>-0.4364657433844437</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06902971543242777</v>
+        <v>-0.0004876583460103334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>78.81381106309314</v>
+        <v>96.50991998789273</v>
       </c>
       <c r="B10" t="n">
-        <v>109.9824677424625</v>
+        <v>103.1117794316368</v>
       </c>
       <c r="C10" t="n">
-        <v>48.81793617580392</v>
+        <v>45.42566571177856</v>
       </c>
       <c r="D10" t="n">
-        <v>10.19487918254972</v>
+        <v>8.609818324029826</v>
       </c>
       <c r="E10" t="n">
-        <v>3.091962891546698</v>
+        <v>4.813275949478117</v>
       </c>
       <c r="F10" t="n">
-        <v>11.27977551157104</v>
+        <v>15.27956640276831</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08998598974487701</v>
+        <v>0.04351574762999324</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6374985070376439</v>
+        <v>-0.7690160030114535</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8162336576705845</v>
+        <v>-0.8730201830554567</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.816378575775174</v>
+        <v>-0.8990214117736538</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.02938862405000105</v>
+        <v>-0.002925038312700844</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4637446643236507</v>
+        <v>-0.5626331799137356</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07935859434478568</v>
+        <v>-0.001963428024414487</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56.5425245981498</v>
+        <v>66.13398614554688</v>
       </c>
       <c r="B11" t="n">
-        <v>113.7361691472359</v>
+        <v>94.50138737276819</v>
       </c>
       <c r="C11" t="n">
-        <v>49.94589612874207</v>
+        <v>45.41899636301677</v>
       </c>
       <c r="D11" t="n">
-        <v>12.45045682948635</v>
+        <v>11.88131775445934</v>
       </c>
       <c r="E11" t="n">
-        <v>2.204105215842724</v>
+        <v>4.497279715791406</v>
       </c>
       <c r="F11" t="n">
-        <v>7.697457257306614</v>
+        <v>9.097221185051708</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3085615554848973</v>
+        <v>0.1676947038216061</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.04074796548152809</v>
+        <v>-0.3156433470575165</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6053261238059665</v>
+        <v>-0.697292479487464</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3315480987616449</v>
+        <v>-0.5749861244074589</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.04596653918998497</v>
+        <v>-0.002196385511604637</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3083724000749896</v>
+        <v>-0.3710048960916017</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.08829060269087473</v>
+        <v>-0.0005082973854768358</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>77.53387227822944</v>
+        <v>97.94232276039587</v>
       </c>
       <c r="B12" t="n">
-        <v>141.9429588369636</v>
+        <v>69.13446697912833</v>
       </c>
       <c r="C12" t="n">
-        <v>48.79755530303289</v>
+        <v>45.42281548229539</v>
       </c>
       <c r="D12" t="n">
-        <v>10.21386838050787</v>
+        <v>8.629107867483402</v>
       </c>
       <c r="E12" t="n">
-        <v>2.210135780609716</v>
+        <v>4.319022693942959</v>
       </c>
       <c r="F12" t="n">
-        <v>11.00264660411453</v>
+        <v>15.6779333570352</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09538516691145131</v>
+        <v>0.04142579068614808</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6199327768721441</v>
+        <v>-0.7784749715209835</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8090986844330446</v>
+        <v>-0.8773668275177239</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8044989129851849</v>
+        <v>-0.9044495871631121</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.002838569708609742</v>
+        <v>-0.05500815801869233</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4541834323506639</v>
+        <v>-0.5728390496678206</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.07796673144409808</v>
+        <v>-0.001341559773540557</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>57.48156076141801</v>
+        <v>85.14927436290208</v>
       </c>
       <c r="B13" t="n">
-        <v>98.9484089760968</v>
+        <v>100.6221814698275</v>
       </c>
       <c r="C13" t="n">
-        <v>48.57547042261232</v>
+        <v>45.41894635677254</v>
       </c>
       <c r="D13" t="n">
-        <v>6.875928668338203</v>
+        <v>10.13984718924091</v>
       </c>
       <c r="E13" t="n">
-        <v>3.745418117133226</v>
+        <v>4.89240174939407</v>
       </c>
       <c r="F13" t="n">
-        <v>7.917495584004696</v>
+        <v>12.73693234659434</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2686988678245001</v>
+        <v>0.06716666220271092</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1018079580315878</v>
+        <v>-0.6688939438233857</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6275144192220741</v>
+        <v>-0.82915253577212</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3901920143249281</v>
+        <v>-0.8373401317223674</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.01390774664328294</v>
+        <v>-0.006351362561748776</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6316811262876413</v>
+        <v>-0.4816885798356773</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.06826578791627284</v>
+        <v>-0.000497386932189342</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98.30876353271749</v>
+        <v>61.41022273194039</v>
       </c>
       <c r="B14" t="n">
-        <v>170.5281549091101</v>
+        <v>102.0548166524822</v>
       </c>
       <c r="C14" t="n">
-        <v>48.81825288415915</v>
+        <v>45.41899636301677</v>
       </c>
       <c r="D14" t="n">
-        <v>7.751953130665252</v>
+        <v>12.49538517808112</v>
       </c>
       <c r="E14" t="n">
-        <v>2.219137847715863</v>
+        <v>4.836732948703573</v>
       </c>
       <c r="F14" t="n">
-        <v>15.51142857919397</v>
+        <v>8.396080658606106</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04156759491953976</v>
+        <v>0.2215230427267476</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8076951377470555</v>
+        <v>-0.1489850006619451</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8911916992231721</v>
+        <v>-0.6416609361397749</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9206599657717721</v>
+        <v>-0.4322860634747148</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1077562333893907</v>
+        <v>-0.01836304689963112</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6093733186536177</v>
+        <v>-0.3355766704895529</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.07938022318349763</v>
+        <v>-0.0005082973854768358</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66.65135272145311</v>
+        <v>95.31148861352256</v>
       </c>
       <c r="B15" t="n">
-        <v>131.6417981217124</v>
+        <v>74.16983982711152</v>
       </c>
       <c r="C15" t="n">
-        <v>49.3142884331707</v>
+        <v>45.54343001197721</v>
       </c>
       <c r="D15" t="n">
-        <v>11.36975581348704</v>
+        <v>8.760970139352033</v>
       </c>
       <c r="E15" t="n">
-        <v>3.986851679869226</v>
+        <v>4.717679047820133</v>
       </c>
       <c r="F15" t="n">
-        <v>9.104458993185515</v>
+        <v>14.99722309858238</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1661091063409743</v>
+        <v>0.04540944470451875</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4090026011452517</v>
+        <v>-0.7606162688992686</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.728843106905724</v>
+        <v>-0.8691806449491281</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.648795134393053</v>
+        <v>-0.8941350714544157</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.001058612665134141</v>
+        <v>-0.0008338924099945059</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.372890252424105</v>
+        <v>-0.5540943563713483</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1073497506041668</v>
+        <v>-0.02765745715866436</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>61.94144542724177</v>
+        <v>82.88274326670476</v>
       </c>
       <c r="B16" t="n">
-        <v>113.7361691472359</v>
+        <v>102.1393686129167</v>
       </c>
       <c r="C16" t="n">
-        <v>48.78452485367274</v>
+        <v>45.41899662419794</v>
       </c>
       <c r="D16" t="n">
-        <v>12.45045682948635</v>
+        <v>10.4809884479151</v>
       </c>
       <c r="E16" t="n">
-        <v>2.563034948853717</v>
+        <v>4.774950981126978</v>
       </c>
       <c r="F16" t="n">
-        <v>8.511871994117291</v>
+        <v>12.28219057437088</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2193977506997953</v>
+        <v>0.07391756298550024</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2662857838945432</v>
+        <v>-0.6419597964000306</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6788538909485953</v>
+        <v>-0.8179535165734678</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5317767118497779</v>
+        <v>-0.8195728791064206</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.08371867259739031</v>
+        <v>-0.01862018851301204</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3377069165147915</v>
+        <v>-0.4655395457752715</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.07707684810850911</v>
+        <v>-0.0005083543704600957</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>59.61378031069594</v>
+        <v>62.37098120395758</v>
       </c>
       <c r="B17" t="n">
-        <v>136.6547685994491</v>
+        <v>100.8226660336632</v>
       </c>
       <c r="C17" t="n">
-        <v>48.79512850137419</v>
+        <v>45.41901347132408</v>
       </c>
       <c r="D17" t="n">
-        <v>12.16014024737149</v>
+        <v>12.38080313549892</v>
       </c>
       <c r="E17" t="n">
-        <v>2.108403085874056</v>
+        <v>4.198921401751535</v>
       </c>
       <c r="F17" t="n">
-        <v>8.042545751987678</v>
+        <v>8.536103733420482</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2525865968837628</v>
+        <v>0.2089294719563881</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1793291518666627</v>
+        <v>-0.1870136540844826</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6499120426764033</v>
+        <v>-0.6540656345631627</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4567422763838654</v>
+        <v>-0.4657405300769248</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.001508935095051274</v>
+        <v>-0.01658130146777826</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3203190957862443</v>
+        <v>-0.3427823590296818</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.07780099883617585</v>
+        <v>-0.0005120301070721256</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73.31717845349161</v>
+        <v>60.58403964431085</v>
       </c>
       <c r="B18" t="n">
-        <v>140.3683492867308</v>
+        <v>103.2568385913157</v>
       </c>
       <c r="C18" t="n">
-        <v>48.82968837053696</v>
+        <v>46.10006790229136</v>
       </c>
       <c r="D18" t="n">
-        <v>10.74537087458507</v>
+        <v>12.42351527219098</v>
       </c>
       <c r="E18" t="n">
-        <v>3.77365941189421</v>
+        <v>4.837672081184164</v>
       </c>
       <c r="F18" t="n">
-        <v>10.24532039954821</v>
+        <v>8.281656759481585</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1169099937455343</v>
+        <v>0.2331834919242349</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5527470933816241</v>
+        <v>-0.1143162697305587</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7824846328906419</v>
+        <v>-0.6304841729949064</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.757385742118161</v>
+        <v>-0.401349415851465</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01090293722503938</v>
+        <v>-0.007687634194098149</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4226844354500632</v>
+        <v>-0.3293802973323314</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.08016118234159798</v>
+        <v>-0.1491057241362968</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>61.57986340391103</v>
+        <v>86.44273380216937</v>
       </c>
       <c r="B19" t="n">
-        <v>135.4765175714978</v>
+        <v>92.08373213917446</v>
       </c>
       <c r="C19" t="n">
-        <v>49.03089346679991</v>
+        <v>45.41959001841146</v>
       </c>
       <c r="D19" t="n">
-        <v>11.92917712575306</v>
+        <v>9.995551473638802</v>
       </c>
       <c r="E19" t="n">
-        <v>2.084644866168491</v>
+        <v>4.374743230737633</v>
       </c>
       <c r="F19" t="n">
-        <v>8.324347014650428</v>
+        <v>13.01534739527187</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2234331980153083</v>
+        <v>0.0637009493018349</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2541999179670958</v>
+        <v>-0.683005638216834</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6748848587296745</v>
+        <v>-0.8351066931898024</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5216054081020682</v>
+        <v>-0.8464603256375555</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0009457412558445622</v>
+        <v>-0.009668108765334516</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.335005873587418</v>
+        <v>-0.4909044783404567</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.09202232026670253</v>
+        <v>-0.0006378221988631583</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>72.26045596694044</v>
+        <v>74.32478356950651</v>
       </c>
       <c r="B20" t="n">
-        <v>146.3582951204604</v>
+        <v>105.555504420088</v>
       </c>
       <c r="C20" t="n">
-        <v>48.79351150358347</v>
+        <v>45.42393221790942</v>
       </c>
       <c r="D20" t="n">
-        <v>10.9185305023789</v>
+        <v>11.56819096458839</v>
       </c>
       <c r="E20" t="n">
-        <v>2.430722759290691</v>
+        <v>4.804099553324155</v>
       </c>
       <c r="F20" t="n">
-        <v>10.07094184322493</v>
+        <v>10.64716893140628</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1233261323141734</v>
+        <v>0.1094635745734929</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5333671683591441</v>
+        <v>-0.5082035110986033</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.775002434846872</v>
+        <v>-0.7652441094197887</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7433351863577822</v>
+        <v>-0.7251090463342317</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01974321998981619</v>
+        <v>-0.03522106138077321</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4147906447903301</v>
+        <v>-0.4045640829327337</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.07769056984421389</v>
+        <v>-0.001585211180237245</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>87.64966668940669</v>
+        <v>58.76407836241744</v>
       </c>
       <c r="B21" t="n">
-        <v>153.7502318732359</v>
+        <v>106.2624003331964</v>
       </c>
       <c r="C21" t="n">
-        <v>48.80623394002838</v>
+        <v>45.42242193876312</v>
       </c>
       <c r="D21" t="n">
-        <v>8.938055315580582</v>
+        <v>12.7093999539209</v>
       </c>
       <c r="E21" t="n">
-        <v>3.999413899124757</v>
+        <v>4.841317111729771</v>
       </c>
       <c r="F21" t="n">
-        <v>13.02740270533969</v>
+        <v>7.999245715504523</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06165248266823558</v>
+        <v>0.2615481302746683</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7332850689543798</v>
+        <v>-0.0310417749334056</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8569948911392521</v>
+        <v>-0.6041480817388071</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8777166965120278</v>
+        <v>-0.3254316965494387</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.005445387048755797</v>
+        <v>-0.008191987992906078</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5297491219758989</v>
+        <v>-0.3157305877181308</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.07855941817534196</v>
+        <v>-0.001255695730137119</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>62.94837051464542</v>
+        <v>81.97138844916053</v>
       </c>
       <c r="B22" t="n">
-        <v>141.9193313214897</v>
+        <v>74.04751610016505</v>
       </c>
       <c r="C22" t="n">
-        <v>48.79767528171592</v>
+        <v>45.42005649846333</v>
       </c>
       <c r="D22" t="n">
-        <v>11.92917712575306</v>
+        <v>10.12451319868309</v>
       </c>
       <c r="E22" t="n">
-        <v>2.074150892004201</v>
+        <v>4.86216891430352</v>
       </c>
       <c r="F22" t="n">
-        <v>8.558208845952773</v>
+        <v>11.98242082581064</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2058674389412679</v>
+        <v>0.07670541442434754</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3007938288514291</v>
+        <v>-0.6338889950921489</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6907459609633391</v>
+        <v>-0.8155743476887568</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5608859660369234</v>
+        <v>-0.8145927937224197</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.01958055439222751</v>
+        <v>-0.03089588840485313</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3452287171305229</v>
+        <v>-0.4479065005363777</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.07797492510094764</v>
+        <v>-0.0007395996647267811</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>94.6629787248534</v>
+        <v>73.7776530689752</v>
       </c>
       <c r="B23" t="n">
-        <v>160.4222652818116</v>
+        <v>83.53871851799957</v>
       </c>
       <c r="C23" t="n">
-        <v>47.67178649839176</v>
+        <v>45.41797687465986</v>
       </c>
       <c r="D23" t="n">
-        <v>8.472981184089727</v>
+        <v>11.30674693185049</v>
       </c>
       <c r="E23" t="n">
-        <v>2.14557139876562</v>
+        <v>4.709025033022856</v>
       </c>
       <c r="F23" t="n">
-        <v>14.71076064222374</v>
+        <v>10.46812052608362</v>
       </c>
       <c r="G23" t="n">
-        <v>0.04731952192445894</v>
+        <v>0.1122428309258954</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7858570964954628</v>
+        <v>-0.5028904749266569</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8808471084980415</v>
+        <v>-0.7644563643662199</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9085314040723943</v>
+        <v>-0.7218991332629858</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1092628881294992</v>
+        <v>-0.0549322488774603</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5821390519185156</v>
+        <v>-0.428332398017314</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.08487987363403542</v>
+        <v>-0.0002858635621520722</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>82.30254096247045</v>
+        <v>59.04246567634544</v>
       </c>
       <c r="B24" t="n">
-        <v>196.5769267064127</v>
+        <v>105.7945759237766</v>
       </c>
       <c r="C24" t="n">
-        <v>48.79343342268375</v>
+        <v>45.41793057499418</v>
       </c>
       <c r="D24" t="n">
-        <v>10.21386838050787</v>
+        <v>12.78496271865454</v>
       </c>
       <c r="E24" t="n">
-        <v>4.132074179577321</v>
+        <v>4.872218769939299</v>
       </c>
       <c r="F24" t="n">
-        <v>12.07206677143923</v>
+        <v>8.063833790479261</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07723127388470451</v>
+        <v>0.2570972412071355</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6800304672502221</v>
+        <v>-0.04436555718109401</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8338888231169131</v>
+        <v>-0.6083038719078437</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8443504138417538</v>
+        <v>-0.3377143247516927</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1135812927049546</v>
+        <v>-0.02422019951739494</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.4898057199409272</v>
+        <v>-0.3178184925725908</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.07768523749614516</v>
+        <v>-0.0002757618169130227</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>75.79254956146076</v>
+        <v>93.97479615330022</v>
       </c>
       <c r="B25" t="n">
-        <v>168.787614817994</v>
+        <v>60.64112799507892</v>
       </c>
       <c r="C25" t="n">
-        <v>49.02724385186119</v>
+        <v>45.42231579732849</v>
       </c>
       <c r="D25" t="n">
-        <v>10.50051664241692</v>
+        <v>8.625745180865302</v>
       </c>
       <c r="E25" t="n">
-        <v>2.198488073504175</v>
+        <v>4.878859982891312</v>
       </c>
       <c r="F25" t="n">
-        <v>10.71241301841351</v>
+        <v>14.60063009726319</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1036394225021853</v>
+        <v>0.04759571685542474</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5939229512075993</v>
+        <v>-0.7527290662479679</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7986444776815588</v>
+        <v>-0.8662301552530425</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7865532435069734</v>
+        <v>-0.889694833841053</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.02268135921517738</v>
+        <v>-0.004455421296177013</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4411756302340725</v>
+        <v>-0.03217527352732434</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.09186030318947619</v>
+        <v>-0.001232537598942623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>84.91885423587834</v>
+        <v>63.94157787703264</v>
       </c>
       <c r="B26" t="n">
-        <v>155.6901410850489</v>
+        <v>99.85303440552144</v>
       </c>
       <c r="C26" t="n">
-        <v>48.78461551543204</v>
+        <v>45.43424621818603</v>
       </c>
       <c r="D26" t="n">
-        <v>10.02596700351958</v>
+        <v>12.44491574526183</v>
       </c>
       <c r="E26" t="n">
-        <v>3.833305936063744</v>
+        <v>4.060351564033477</v>
       </c>
       <c r="F26" t="n">
-        <v>12.63836837275702</v>
+        <v>8.83331356313424</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06915470894555313</v>
+        <v>0.1906184761371723</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7076069435006483</v>
+        <v>-0.2442021340663454</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8456785848722427</v>
+        <v>-0.6729976159486051</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8618620899859398</v>
+        <v>-0.5150476595664161</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1430418133128075</v>
+        <v>-0.02651277959401874</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5093497625286525</v>
+        <v>-0.3425727882258012</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.07708303963625719</v>
+        <v>-0.003835538513313891</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>85.65534701117311</v>
+        <v>71.28089514314892</v>
       </c>
       <c r="B27" t="n">
-        <v>155.6901410850489</v>
+        <v>109.010881391453</v>
       </c>
       <c r="C27" t="n">
-        <v>48.79757837523298</v>
+        <v>45.41961706611573</v>
       </c>
       <c r="D27" t="n">
-        <v>10.04712926894918</v>
+        <v>11.98794436829041</v>
       </c>
       <c r="E27" t="n">
-        <v>3.843740362130629</v>
+        <v>4.711268779346149</v>
       </c>
       <c r="F27" t="n">
-        <v>12.8206522531113</v>
+        <v>10.12328082411032</v>
       </c>
       <c r="G27" t="n">
-        <v>0.06711359778736843</v>
+        <v>0.1276232943944806</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7147488561878225</v>
+        <v>-0.444107839453878</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8487690440150196</v>
+        <v>-0.7413593049344394</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8663086546366269</v>
+        <v>-0.6765540554189072</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1645445433853825</v>
+        <v>-0.04868428258464452</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5148514149157017</v>
+        <v>-0.3828763778949361</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.07796830710475308</v>
+        <v>-0.0006437235161614596</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>68.9353978251372</v>
+        <v>72.63384399891086</v>
       </c>
       <c r="B28" t="n">
-        <v>192.9648513566074</v>
+        <v>109.027191447263</v>
       </c>
       <c r="C28" t="n">
-        <v>48.81521029202682</v>
+        <v>45.41932186706686</v>
       </c>
       <c r="D28" t="n">
-        <v>11.17789312644696</v>
+        <v>11.73339419217748</v>
       </c>
       <c r="E28" t="n">
-        <v>3.638875245140883</v>
+        <v>4.494918356680505</v>
       </c>
       <c r="F28" t="n">
-        <v>9.478508612440349</v>
+        <v>10.33609339594366</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1465954091996605</v>
+        <v>0.1190438403556735</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4645624557221757</v>
+        <v>-0.4739783626356189</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.749114538313444</v>
+        <v>-0.752405811663735</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6919428334573383</v>
+        <v>-0.6994345057862282</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.0004419847995036891</v>
+        <v>-0.03149653068531479</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.389952228614954</v>
+        <v>-0.3925161384922399</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.07917243663978642</v>
+        <v>-0.0005793164509497462</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>59.87941324513776</v>
+        <v>89.75658751085793</v>
       </c>
       <c r="B29" t="n">
-        <v>158.0603336608038</v>
+        <v>134.3992626536376</v>
       </c>
       <c r="C29" t="n">
-        <v>49.47592055459435</v>
+        <v>45.42241024197128</v>
       </c>
       <c r="D29" t="n">
-        <v>12.0699155061401</v>
+        <v>10.00286885752524</v>
       </c>
       <c r="E29" t="n">
-        <v>2.667935089208784</v>
+        <v>4.580892959319906</v>
       </c>
       <c r="F29" t="n">
-        <v>8.088732495352014</v>
+        <v>13.84276187999067</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2484283212378303</v>
+        <v>0.05595547124983367</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1899770071400672</v>
+        <v>-0.7154457007316766</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6534151842779057</v>
+        <v>-0.8490186647511434</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4660848235392042</v>
+        <v>-0.8669023402666554</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.004752913886607322</v>
+        <v>-0.09338835204348377</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.3223033923290935</v>
+        <v>-0.5145156860148627</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1070043999099785</v>
+        <v>-0.001253143702825282</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>93.12930784292035</v>
+        <v>63.94157787703264</v>
       </c>
       <c r="B30" t="n">
-        <v>116.7479450999329</v>
+        <v>99.82441789075537</v>
       </c>
       <c r="C30" t="n">
-        <v>48.6549455959893</v>
+        <v>45.43424621818603</v>
       </c>
       <c r="D30" t="n">
-        <v>8.462088511955193</v>
+        <v>12.44491574526183</v>
       </c>
       <c r="E30" t="n">
-        <v>2.313986026303247</v>
+        <v>4.060351564033477</v>
       </c>
       <c r="F30" t="n">
-        <v>14.30374817843847</v>
+        <v>8.83331356313424</v>
       </c>
       <c r="G30" t="n">
-        <v>0.05000718788703062</v>
+        <v>0.1906184761371723</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7757057539303673</v>
+        <v>-0.2442021340663454</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8761484864360392</v>
+        <v>-0.6729976159486051</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.902758215255324</v>
+        <v>-0.5150476595664161</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.07295901124069083</v>
+        <v>-0.02651277959401874</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.5706824234876967</v>
+        <v>-0.3425727882258012</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.07100057616977036</v>
+        <v>-0.003835538513313891</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>84.11755202242153</v>
+        <v>60.28933311754266</v>
       </c>
       <c r="B31" t="n">
-        <v>110.9869958884489</v>
+        <v>103.4490252912484</v>
       </c>
       <c r="C31" t="n">
-        <v>48.78478828556973</v>
+        <v>45.41855790355955</v>
       </c>
       <c r="D31" t="n">
-        <v>9.487203498450659</v>
+        <v>12.6261000030493</v>
       </c>
       <c r="E31" t="n">
-        <v>4.184443144875867</v>
+        <v>4.886872799309445</v>
       </c>
       <c r="F31" t="n">
-        <v>12.31295516737049</v>
+        <v>8.235262625272759</v>
       </c>
       <c r="G31" t="n">
-        <v>0.07129313708096958</v>
+        <v>0.2374942117257215</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.699745001759593</v>
+        <v>-0.1015075085240597</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8423538275824579</v>
+        <v>-0.6263894627870055</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8569470332822279</v>
+        <v>-0.3898203013392023</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.02158352330268976</v>
+        <v>-0.0200932040941258</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.5033639791193746</v>
+        <v>-0.32716999838157</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.07709483855908492</v>
+        <v>-0.0004126335039025819</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>67.63362767352608</v>
+        <v>80.75351127546278</v>
       </c>
       <c r="B32" t="n">
-        <v>170.2298528424951</v>
+        <v>74.04751610016505</v>
       </c>
       <c r="C32" t="n">
-        <v>48.85543762243103</v>
+        <v>45.41802076905515</v>
       </c>
       <c r="D32" t="n">
-        <v>11.69713295450874</v>
+        <v>10.12599731362433</v>
       </c>
       <c r="E32" t="n">
-        <v>2.209916764681309</v>
+        <v>4.58116434629092</v>
       </c>
       <c r="F32" t="n">
-        <v>9.361960738376206</v>
+        <v>11.70250464043106</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1577301567939385</v>
+        <v>0.08084962077121864</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4334631735139727</v>
+        <v>-0.6177224147757423</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7376272644744613</v>
+        <v>-0.8090446584372522</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6679143226059665</v>
+        <v>-0.8036752550601778</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.06467680257463046</v>
+        <v>-9.073253150794426e-05</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.3802279148100638</v>
+        <v>-0.4806513345659709</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.08191966583906446</v>
+        <v>-0.0002954405211258448</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>76.27442103470223</v>
+        <v>61.77596147811725</v>
       </c>
       <c r="B33" t="n">
-        <v>197.6773756549914</v>
+        <v>101.8242403502885</v>
       </c>
       <c r="C33" t="n">
-        <v>48.92277722820317</v>
+        <v>45.43407541472983</v>
       </c>
       <c r="D33" t="n">
-        <v>10.39116333040885</v>
+        <v>12.4960617292446</v>
       </c>
       <c r="E33" t="n">
-        <v>2.614753438442711</v>
+        <v>4.209164608039109</v>
       </c>
       <c r="F33" t="n">
-        <v>10.78204895003035</v>
+        <v>8.460957642778439</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1012398152633595</v>
+        <v>0.2166886817516443</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6013809110569142</v>
+        <v>-0.1637033942790315</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8016293384397418</v>
+        <v>-0.6464367206917224</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7917417157510854</v>
+        <v>-0.4452877975109536</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.01073369030315257</v>
+        <v>-0.02492771647496399</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.4447752437400555</v>
+        <v>-0.3383197110858794</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0865184629599821</v>
+        <v>-0.003798272304689765</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>56.22689781959032</v>
+        <v>88.00782820561535</v>
       </c>
       <c r="B34" t="n">
-        <v>145.2090827399065</v>
+        <v>123.8191537946786</v>
       </c>
       <c r="C34" t="n">
-        <v>49.03104087367529</v>
+        <v>45.41802076905515</v>
       </c>
       <c r="D34" t="n">
-        <v>12.48639214167455</v>
+        <v>10.12588420469578</v>
       </c>
       <c r="E34" t="n">
-        <v>2.313986026303247</v>
+        <v>4.459791368789547</v>
       </c>
       <c r="F34" t="n">
-        <v>7.579647021856762</v>
+        <v>13.43321707731214</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3155323717563421</v>
+        <v>0.05990477139180368</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.02452918090200298</v>
+        <v>-0.6988835548038086</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6001914765238222</v>
+        <v>-0.8418550471772798</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.316424755760876</v>
+        <v>-0.8565509556799018</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.004804039614122089</v>
+        <v>-0.07281681290760747</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.2950188474105712</v>
+        <v>-0.5020557759650093</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.0920324907391068</v>
+        <v>-0.0002954405211258448</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>65.6021835362409</v>
+        <v>87.52556849504624</v>
       </c>
       <c r="B35" t="n">
-        <v>144.9222621844868</v>
+        <v>66.1002646875306</v>
       </c>
       <c r="C35" t="n">
-        <v>48.79767528171592</v>
+        <v>45.41789611426849</v>
       </c>
       <c r="D35" t="n">
-        <v>11.9212824378004</v>
+        <v>10.13505662760159</v>
       </c>
       <c r="E35" t="n">
-        <v>2.074150892004201</v>
+        <v>4.581850692774544</v>
       </c>
       <c r="F35" t="n">
-        <v>9.034974039138834</v>
+        <v>13.3157849447193</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1766953995231978</v>
+        <v>0.06105413179590524</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.38044216449725</v>
+        <v>-0.6968211247911386</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7185439702637052</v>
+        <v>-0.8417490015665222</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.6260194602380021</v>
+        <v>-0.8555505605024433</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.06365510845909356</v>
+        <v>-0.1741598691667628</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.365052885452065</v>
+        <v>-0.2072253652146629</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.07797492510094764</v>
+        <v>-0.0002682431131249829</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67.58818198542602</v>
+        <v>66.96188445390929</v>
       </c>
       <c r="B36" t="n">
-        <v>164.301211050248</v>
+        <v>94.27081107057448</v>
       </c>
       <c r="C36" t="n">
-        <v>48.67004820040149</v>
+        <v>45.43407541472983</v>
       </c>
       <c r="D36" t="n">
-        <v>11.33977286707993</v>
+        <v>11.87829049155561</v>
       </c>
       <c r="E36" t="n">
-        <v>2.431886001082806</v>
+        <v>4.03886307780123</v>
       </c>
       <c r="F36" t="n">
-        <v>9.269232421024679</v>
+        <v>9.253223147846949</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1577818014383262</v>
+        <v>0.1602072177854995</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4326433387077862</v>
+        <v>-0.3401152791921763</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7373927999665324</v>
+        <v>-0.7057487304972747</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6673162943535565</v>
+        <v>-0.5950363765146537</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.0003089509403684793</v>
+        <v>-0.01737857821133517</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.3798884323510313</v>
+        <v>-0.3772141334043198</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.07163589449799622</v>
+        <v>-0.003798272304689765</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>96.89426998856982</v>
+        <v>72.22315730520879</v>
       </c>
       <c r="B37" t="n">
-        <v>174.4960518981925</v>
+        <v>86.66471938858442</v>
       </c>
       <c r="C37" t="n">
-        <v>48.81787470739119</v>
+        <v>45.41737843230329</v>
       </c>
       <c r="D37" t="n">
-        <v>7.751953130665252</v>
+        <v>11.36933407929252</v>
       </c>
       <c r="E37" t="n">
-        <v>2.213102039781575</v>
+        <v>4.470040963518388</v>
       </c>
       <c r="F37" t="n">
-        <v>15.12393190952176</v>
+        <v>10.1625799195254</v>
       </c>
       <c r="G37" t="n">
-        <v>0.04363015380698234</v>
+        <v>0.1212474584191642</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7996673944631456</v>
+        <v>-0.4710792827887841</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8873790513715351</v>
+        <v>-0.7526242353480789</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.916256647916362</v>
+        <v>-0.6980579865555762</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.05083682825413837</v>
+        <v>-0.03380306461861618</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.5988069532462842</v>
+        <v>-0.4166736797890659</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.07935439650673431</v>
+        <v>-0.0001552943207196178</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>80.01864620598793</v>
+        <v>77.879101141061</v>
       </c>
       <c r="B38" t="n">
-        <v>141.9600788319887</v>
+        <v>129.2952901061263</v>
       </c>
       <c r="C38" t="n">
-        <v>48.79851487270207</v>
+        <v>45.41759932510906</v>
       </c>
       <c r="D38" t="n">
-        <v>10.21386838050787</v>
+        <v>11.01876715839579</v>
       </c>
       <c r="E38" t="n">
-        <v>2.20361664383827</v>
+        <v>4.813913624888698</v>
       </c>
       <c r="F38" t="n">
-        <v>11.55208075198127</v>
+        <v>11.2768181599742</v>
       </c>
       <c r="G38" t="n">
-        <v>0.08528528552631785</v>
+        <v>0.0923414535992278</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6530167206948769</v>
+        <v>-0.5709634342764019</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8226085395223178</v>
+        <v>-0.7894512774241779</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8267159817133307</v>
+        <v>-0.7706657653451217</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.06060461569481933</v>
+        <v>-0.00945944471725995</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.4727448668541576</v>
+        <v>-0.4298885956300595</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.07803226295681386</v>
+        <v>-0.0002034891147047191</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>94.26604387016216</v>
+        <v>89.88512308799352</v>
       </c>
       <c r="B39" t="n">
-        <v>156.4374647861601</v>
+        <v>128.5612860732398</v>
       </c>
       <c r="C39" t="n">
-        <v>47.67178649839176</v>
+        <v>45.42293556882947</v>
       </c>
       <c r="D39" t="n">
-        <v>8.431935072005366</v>
+        <v>10.09354652319955</v>
       </c>
       <c r="E39" t="n">
-        <v>2.414592583044891</v>
+        <v>4.492713092766851</v>
       </c>
       <c r="F39" t="n">
-        <v>14.59517634386185</v>
+        <v>13.89767523752297</v>
       </c>
       <c r="G39" t="n">
-        <v>0.04798838609358658</v>
+        <v>0.05570250667825565</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7833009058687023</v>
+        <v>-0.7165795113712995</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8796619442849296</v>
+        <v>-0.8495029567208996</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.907086734679904</v>
+        <v>-0.8676003652113731</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.08675580415851139</v>
+        <v>-0.1127168829931532</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.5791739208757285</v>
+        <v>-0.5154315020019539</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.08487987363403542</v>
+        <v>-0.001367760471885221</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>60.81463511677796</v>
+        <v>67.8284673161394</v>
       </c>
       <c r="B40" t="n">
-        <v>170.3218990224784</v>
+        <v>94.80828634600815</v>
       </c>
       <c r="C40" t="n">
-        <v>48.85084530863138</v>
+        <v>45.41958143074013</v>
       </c>
       <c r="D40" t="n">
-        <v>12.15529581455449</v>
+        <v>11.90880155737262</v>
       </c>
       <c r="E40" t="n">
-        <v>2.385150340918648</v>
+        <v>4.692181727373504</v>
       </c>
       <c r="F40" t="n">
-        <v>8.247763074135976</v>
+        <v>9.424908801096263</v>
       </c>
       <c r="G40" t="n">
-        <v>0.234462242278473</v>
+        <v>0.152860202163884</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.2260252520628915</v>
+        <v>-0.3644599166197824</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6653761454800036</v>
+        <v>-0.7142441944994116</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.497410540478266</v>
+        <v>-0.6147381815126683</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.02157744014040112</v>
+        <v>-0.006775792329338096</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.3292895649232112</v>
+        <v>-0.3709956672492694</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.08160604476513568</v>
+        <v>-0.0006359485251185293</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>60.81463511677796</v>
+        <v>75.5092819755011</v>
       </c>
       <c r="B41" t="n">
-        <v>170.2068492454665</v>
+        <v>90.11533499762007</v>
       </c>
       <c r="C41" t="n">
-        <v>48.85084530863138</v>
+        <v>45.41793870108359</v>
       </c>
       <c r="D41" t="n">
-        <v>12.15529581455449</v>
+        <v>11.30034953152783</v>
       </c>
       <c r="E41" t="n">
-        <v>2.385150340918648</v>
+        <v>4.330798302603925</v>
       </c>
       <c r="F41" t="n">
-        <v>8.247763074135976</v>
+        <v>10.83200848662022</v>
       </c>
       <c r="G41" t="n">
-        <v>0.234462242278473</v>
+        <v>0.103268296146617</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.2260252520628915</v>
+        <v>-0.5304951888489267</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6653761454800036</v>
+        <v>-0.7737575868460346</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.497410540478266</v>
+        <v>-0.7415326928017218</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.02157744014040112</v>
+        <v>-0.0119798514542138</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.3292895649232112</v>
+        <v>-0.4130036340754453</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.08160604476513568</v>
+        <v>-0.0002775347818732843</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96.89426998856982</v>
+        <v>94.19350826672959</v>
       </c>
       <c r="B42" t="n">
-        <v>179.2023435008956</v>
+        <v>54.67803555457682</v>
       </c>
       <c r="C42" t="n">
-        <v>48.81787470739119</v>
+        <v>45.42231579732849</v>
       </c>
       <c r="D42" t="n">
-        <v>7.751953130665252</v>
+        <v>8.625745180865302</v>
       </c>
       <c r="E42" t="n">
-        <v>2.213746421968519</v>
+        <v>4.878859982891312</v>
       </c>
       <c r="F42" t="n">
-        <v>15.12393190952176</v>
+        <v>14.65881116607977</v>
       </c>
       <c r="G42" t="n">
-        <v>0.04363015380698234</v>
+        <v>0.04722364707611051</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.7996673944631456</v>
+        <v>-0.7543597801544533</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.8873790513715351</v>
+        <v>-0.8669617576521879</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.916256647916362</v>
+        <v>-0.8906551538826075</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.05083682825413837</v>
+        <v>-0.01193642679251755</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5988069532462842</v>
+        <v>-0.02294076207141745</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.07935439650673431</v>
+        <v>-0.001232537598942623</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>64.29035018960447</v>
+        <v>59.65216883334374</v>
       </c>
       <c r="B43" t="n">
-        <v>168.9818750251465</v>
+        <v>103.3627349943248</v>
       </c>
       <c r="C43" t="n">
-        <v>49.0310671394415</v>
+        <v>45.41800662400216</v>
       </c>
       <c r="D43" t="n">
-        <v>11.69015192858625</v>
+        <v>12.6261000030493</v>
       </c>
       <c r="E43" t="n">
-        <v>2.349530028028424</v>
+        <v>4.309579417241707</v>
       </c>
       <c r="F43" t="n">
-        <v>8.742968576135157</v>
+        <v>8.127185357533541</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1901052317281058</v>
+        <v>0.2471128002503656</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.3429359617809006</v>
+        <v>-0.07297501125149702</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.7053855684064404</v>
+        <v>-0.6173318072893539</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.5957066288964045</v>
+        <v>-0.3639484115337493</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.007749864220438839</v>
+        <v>-0.009604199680339322</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.3552533988786299</v>
+        <v>-0.3223912662500781</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.09203430296970784</v>
+        <v>-0.0002923543277449925</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>63.2909221930414</v>
+        <v>67.9726231609111</v>
       </c>
       <c r="B44" t="n">
-        <v>174.4751705152477</v>
+        <v>100.8226660336632</v>
       </c>
       <c r="C44" t="n">
-        <v>48.79211583282917</v>
+        <v>46.27627513985092</v>
       </c>
       <c r="D44" t="n">
-        <v>12.1421930345954</v>
+        <v>12.25106236794795</v>
       </c>
       <c r="E44" t="n">
-        <v>2.385150340918648</v>
+        <v>4.180929599284394</v>
       </c>
       <c r="F44" t="n">
-        <v>8.67207160816033</v>
+        <v>9.593204509943561</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2020668382425721</v>
+        <v>0.1522308042074159</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3115844993687688</v>
+        <v>-0.3607731911779966</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.6944115506870892</v>
+        <v>-0.7113696246084207</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.5698233400554031</v>
+        <v>-0.6106044735265609</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.05913048636275172</v>
+        <v>-0.05185447184232676</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.3477876020542492</v>
+        <v>-0.3593049400214915</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.07759525585220256</v>
+        <v>-0.1875509396038379</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>70.34337958173715</v>
+        <v>59.67924501225068</v>
       </c>
       <c r="B45" t="n">
-        <v>174.3748240905999</v>
+        <v>106.8650037761644</v>
       </c>
       <c r="C45" t="n">
-        <v>47.34638320685202</v>
+        <v>45.42240160019094</v>
       </c>
       <c r="D45" t="n">
-        <v>11.25848295189065</v>
+        <v>12.73550107390722</v>
       </c>
       <c r="E45" t="n">
-        <v>2.516632887434865</v>
+        <v>4.841317111729771</v>
       </c>
       <c r="F45" t="n">
-        <v>9.761921281022387</v>
+        <v>8.158886785136204</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1362191260659843</v>
+        <v>0.2468917621139214</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4951662976373878</v>
+        <v>-0.07411511670666929</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.760487819974887</v>
+        <v>-0.6176757189723626</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.7150723348222976</v>
+        <v>-0.3649699077962811</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.01207566503372215</v>
+        <v>-0.002918640236162344</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.4004699505152396</v>
+        <v>-0.311404479152083</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.08372088349114724</v>
+        <v>-0.00125125822347763</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>81.32287879399537</v>
+        <v>67.1709203707649</v>
       </c>
       <c r="B46" t="n">
-        <v>191.9312470855912</v>
+        <v>94.27081107057448</v>
       </c>
       <c r="C46" t="n">
-        <v>49.66337855964839</v>
+        <v>45.43407541472983</v>
       </c>
       <c r="D46" t="n">
-        <v>9.825203138539505</v>
+        <v>11.86678248426004</v>
       </c>
       <c r="E46" t="n">
-        <v>2.697027792552511</v>
+        <v>4.03886307780123</v>
       </c>
       <c r="F46" t="n">
-        <v>11.77876737052173</v>
+        <v>9.29003832713418</v>
       </c>
       <c r="G46" t="n">
-        <v>0.08044037589871368</v>
+        <v>0.1583746878151326</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.6689292355968398</v>
+        <v>-0.3461118610137069</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8292569646166521</v>
+        <v>-0.7078351533877888</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.8371740742490086</v>
+        <v>-0.599913472478031</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.03469888417351128</v>
+        <v>-0.01936229612062313</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.4824875752306337</v>
+        <v>-0.3787819027807369</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.1021650368591388</v>
+        <v>-0.003798272304689765</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>68.9353978251372</v>
+        <v>77.45030078644784</v>
       </c>
       <c r="B47" t="n">
-        <v>169.0305154079113</v>
+        <v>123.9881433289821</v>
       </c>
       <c r="C47" t="n">
-        <v>48.81521029202682</v>
+        <v>45.41890176741921</v>
       </c>
       <c r="D47" t="n">
-        <v>11.17789312644696</v>
+        <v>11.05148315767015</v>
       </c>
       <c r="E47" t="n">
-        <v>2.338178049166237</v>
+        <v>4.813913624888698</v>
       </c>
       <c r="F47" t="n">
-        <v>9.478508612440349</v>
+        <v>11.19075862248728</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1465954091996605</v>
+        <v>0.09419046307949076</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.4645624557221757</v>
+        <v>-0.5640158120324928</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.749114538313444</v>
+        <v>-0.7867330379459295</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.6919428334573383</v>
+        <v>-0.7657277206103443</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.0004419847995036891</v>
+        <v>-0.006604942130933504</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.389952228614954</v>
+        <v>-0.4268333931034408</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.07917243663978642</v>
+        <v>-0.0004876583460103334</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>71.42468541303199</v>
+        <v>81.04504375045758</v>
       </c>
       <c r="B48" t="n">
-        <v>158.2284595176338</v>
+        <v>74.04751610016505</v>
       </c>
       <c r="C48" t="n">
-        <v>49.51481622024488</v>
+        <v>45.42392218024849</v>
       </c>
       <c r="D48" t="n">
-        <v>10.86844092090522</v>
+        <v>10.12512418435838</v>
       </c>
       <c r="E48" t="n">
-        <v>2.667935089208784</v>
+        <v>4.74390074021033</v>
       </c>
       <c r="F48" t="n">
-        <v>9.91397950154265</v>
+        <v>11.76929751924323</v>
       </c>
       <c r="G48" t="n">
-        <v>0.128667047199217</v>
+        <v>0.07983086986937543</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.5172804526007521</v>
+        <v>-0.6216801183465999</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.7688675278736328</v>
+        <v>-0.8106363589626165</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.7315327615531717</v>
+        <v>-0.8063622076192647</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.008079151995581837</v>
+        <v>-0.007479657189142453</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.4085473804744032</v>
+        <v>-0.4828378281284318</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1063374361063648</v>
+        <v>-0.001583021145124819</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>82.86012019860027</v>
+        <v>85.32406227841764</v>
       </c>
       <c r="B49" t="n">
-        <v>111.8839132081993</v>
+        <v>74.16983982711152</v>
       </c>
       <c r="C49" t="n">
-        <v>48.79364245183152</v>
+        <v>45.42103157581549</v>
       </c>
       <c r="D49" t="n">
-        <v>10.49647710122532</v>
+        <v>10.23263482047109</v>
       </c>
       <c r="E49" t="n">
-        <v>4.061865961964569</v>
+        <v>4.712504130065279</v>
       </c>
       <c r="F49" t="n">
-        <v>12.27231914268298</v>
+        <v>12.80192893949977</v>
       </c>
       <c r="G49" t="n">
-        <v>0.07552891582116668</v>
+        <v>0.06671812224803117</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.6860703925905987</v>
+        <v>-0.6708037571807597</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.8364121056987359</v>
+        <v>-0.829941581176778</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.8482156897865972</v>
+        <v>-0.8385767295232811</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.1728477106621528</v>
+        <v>-0.02844611505401459</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.4939708757147837</v>
+        <v>-0.4829339437337257</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.07769951264123916</v>
+        <v>-0.0009523438142884644</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>70.34337958173715</v>
+        <v>82.56009426029243</v>
       </c>
       <c r="B50" t="n">
-        <v>173.3948995280861</v>
+        <v>128.4427867065539</v>
       </c>
       <c r="C50" t="n">
-        <v>47.34638320685202</v>
+        <v>45.42370926216537</v>
       </c>
       <c r="D50" t="n">
-        <v>11.25848295189065</v>
+        <v>10.73650345286686</v>
       </c>
       <c r="E50" t="n">
-        <v>2.520916937823204</v>
+        <v>4.645071839590406</v>
       </c>
       <c r="F50" t="n">
-        <v>9.761921281022387</v>
+        <v>12.26966791865125</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1362191260659843</v>
+        <v>0.0750284602076471</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4951662976373878</v>
+        <v>-0.6377833657048784</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.760487819974887</v>
+        <v>-0.816210609567952</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.7150723348222976</v>
+        <v>-0.8167655510949124</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01207566503372215</v>
+        <v>-0.0578299510557789</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.4004699505152396</v>
+        <v>-0.4632406716045836</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.08372088349114724</v>
+        <v>-0.001536566290627484</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>93.12930784292035</v>
+        <v>98.85824860271453</v>
       </c>
       <c r="B51" t="n">
-        <v>116.7479450999329</v>
+        <v>95.25206590173381</v>
       </c>
       <c r="C51" t="n">
-        <v>48.6549455959893</v>
+        <v>45.42109302209567</v>
       </c>
       <c r="D51" t="n">
-        <v>8.462088511955193</v>
+        <v>8.760970139352033</v>
       </c>
       <c r="E51" t="n">
-        <v>2.446224708295872</v>
+        <v>4.625829730040961</v>
       </c>
       <c r="F51" t="n">
-        <v>14.30374817843847</v>
+        <v>15.96502458894707</v>
       </c>
       <c r="G51" t="n">
-        <v>0.05000718788703062</v>
+        <v>0.04017769787784395</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.7757057539303673</v>
+        <v>-0.7842167615926746</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8761484864360392</v>
+        <v>-0.8800182797818965</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.902758215255324</v>
+        <v>-0.9077057327973757</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.07295901124069083</v>
+        <v>-0.112751362276573</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5706824234876967</v>
+        <v>-0.5793650212943409</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.07100057616977036</v>
+        <v>-0.0009657502754191472</v>
       </c>
     </row>
   </sheetData>
